--- a/TRABAJOFINAL/datos_colombia_dashboard.xlsx
+++ b/TRABAJOFINAL/datos_colombia_dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB4C6CB6-94B8-4BC8-8658-8437E5CCE1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C6BB807-6A4F-48E8-BF48-F52413464A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -869,7 +869,7 @@
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -895,7 +895,7 @@
         <v>14</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -927,7 +927,7 @@
         <v>23</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -953,7 +953,7 @@
         <v>23</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -979,7 +979,7 @@
         <v>14</v>
       </c>
       <c r="J6" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1005,7 +1005,7 @@
         <v>14</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1037,7 +1037,7 @@
         <v>14</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1069,7 +1069,7 @@
         <v>43</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1101,7 +1101,7 @@
         <v>43</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1127,7 +1127,7 @@
         <v>14</v>
       </c>
       <c r="J11" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1153,7 +1153,7 @@
         <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1179,7 +1179,7 @@
         <v>14</v>
       </c>
       <c r="J13" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1211,7 +1211,7 @@
         <v>14</v>
       </c>
       <c r="J14" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -1243,7 +1243,7 @@
         <v>63</v>
       </c>
       <c r="J15" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -1275,7 +1275,7 @@
         <v>14</v>
       </c>
       <c r="J16" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -1301,7 +1301,7 @@
         <v>14</v>
       </c>
       <c r="J17" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -1327,7 +1327,7 @@
         <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -1353,7 +1353,7 @@
         <v>14</v>
       </c>
       <c r="J19" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -1379,7 +1379,7 @@
         <v>83</v>
       </c>
       <c r="J20" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -1411,7 +1411,7 @@
         <v>43</v>
       </c>
       <c r="J21" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -1437,7 +1437,7 @@
         <v>43</v>
       </c>
       <c r="J22" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -1463,7 +1463,7 @@
         <v>14</v>
       </c>
       <c r="J23" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -1489,7 +1489,7 @@
         <v>14</v>
       </c>
       <c r="J24" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -1515,7 +1515,7 @@
         <v>14</v>
       </c>
       <c r="J25" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1541,7 +1541,7 @@
         <v>14</v>
       </c>
       <c r="J26" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1573,7 +1573,7 @@
         <v>105</v>
       </c>
       <c r="J27" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1599,7 +1599,7 @@
         <v>14</v>
       </c>
       <c r="J28" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1625,7 +1625,7 @@
         <v>14</v>
       </c>
       <c r="J29" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1651,7 +1651,7 @@
         <v>43</v>
       </c>
       <c r="J30" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1683,7 +1683,7 @@
         <v>14</v>
       </c>
       <c r="J31" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -1715,7 +1715,7 @@
         <v>14</v>
       </c>
       <c r="J32" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1747,7 +1747,7 @@
         <v>14</v>
       </c>
       <c r="J33" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1779,7 +1779,7 @@
         <v>14</v>
       </c>
       <c r="J34" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1811,7 +1811,7 @@
         <v>14</v>
       </c>
       <c r="J35" t="s">
-        <v>127</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -1843,7 +1843,7 @@
         <v>23</v>
       </c>
       <c r="J36" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -1875,7 +1875,7 @@
         <v>23</v>
       </c>
       <c r="J37" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -1907,7 +1907,7 @@
         <v>23</v>
       </c>
       <c r="J38" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -1939,7 +1939,7 @@
         <v>23</v>
       </c>
       <c r="J39" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -1971,7 +1971,7 @@
         <v>23</v>
       </c>
       <c r="J40" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2003,7 +2003,7 @@
         <v>14</v>
       </c>
       <c r="J41" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2035,7 +2035,7 @@
         <v>43</v>
       </c>
       <c r="J42" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
